--- a/evaluation_forms/004_mrr_evaluation_form--evaluation_forms.xlsx
+++ b/evaluation_forms/004_mrr_evaluation_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -909,12 +909,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'october'}</t>
+          <t>october</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'October'}</t>
+          <t>October</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'november'}</t>
+          <t>november</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'November'}</t>
+          <t>November</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'december'}</t>
+          <t>december</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'December'}</t>
+          <t>December</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_2022}</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 2022}</t>
+          <t>2022</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_2023}</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 2023}</t>
+          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_2024}</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 2024}</t>
+          <t>2024</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'increase_in_average_revenue_per_user_(arpu)'}</t>
+          <t>increase_in_average_revenue_per_user_(arpu)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Increase in Average Revenue Per User (ARPU)'}</t>
+          <t>Increase in Average Revenue Per User (ARPU)</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'increase_in_user_growth'}</t>
+          <t>increase_in_user_growth</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Increase in User Growth'}</t>
+          <t>Increase in User Growth</t>
         </is>
       </c>
     </row>
@@ -1198,12 +1198,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'increase_in_average_revenue_per_user_(arpu)_and_increase_in_user_growth'}</t>
+          <t>increase_in_average_revenue_per_user_(arpu)_and_increase_in_user_growth</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Increase in Average Revenue Per User (ARPU) and Increase in User Growth'}</t>
+          <t>Increase in Average Revenue Per User (ARPU) and Increase in User Growth</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'other_(please_specify)'}</t>
+          <t>other_(please_specify)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Other (please specify)'}</t>
+          <t>Other (please specify)</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'ChatJIMMY'}</t>
+          <t>ChatJIMMY</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1266,12 +1266,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'chatjimmy'}</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'ChatJIMMY'}</t>
+          <t>ChatJIMMY</t>
         </is>
       </c>
     </row>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
